--- a/批量导入用户测试.xlsx
+++ b/批量导入用户测试.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21710" windowHeight="10520"/>
+    <workbookView windowWidth="21710" windowHeight="11120"/>
   </bookViews>
   <sheets>
     <sheet name="批量导入用户测试" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
     <t>姓名</t>
   </si>
@@ -44,7 +44,7 @@
     <t>初始密码</t>
   </si>
   <si>
-    <t>测试组员1</t>
+    <t>测试组员a</t>
   </si>
   <si>
     <t>测试组</t>
@@ -53,22 +53,7 @@
     <t>user</t>
   </si>
   <si>
-    <t>测试组员2</t>
-  </si>
-  <si>
-    <t>测试组长</t>
-  </si>
-  <si>
-    <t>leader</t>
-  </si>
-  <si>
-    <t>测试管理员</t>
-  </si>
-  <si>
-    <t>0000002</t>
-  </si>
-  <si>
-    <t>admin</t>
+    <t>测试组员b</t>
   </si>
 </sst>
 </file>
@@ -686,9 +671,6 @@
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1224,8 +1206,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="4"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
@@ -1249,7 +1231,7 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>1234567</v>
+        <v>11111111</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -1263,7 +1245,7 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>1234568</v>
+        <v>2222222</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1272,37 +1254,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>1234569</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
